--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_25_R3.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_25_R3.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8485</v>
+        <v>7.7773</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9506</v>
+        <v>7.8458</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1021</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>4.568</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0486</v>
+        <v>-0.0226</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7774</v>
+        <v>0.6726</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7288</v>
+        <v>-0.6952</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.1158</v>
+        <v>6.0885</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6116</v>
+        <v>2.786</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5041</v>
+        <v>3.3025</v>
       </c>
       <c r="G3" t="n">
         <v>2.1346</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1589</v>
+        <v>0.1316</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8259</v>
+        <v>0.0002</v>
       </c>
       <c r="U3" t="n">
-        <v>0.333</v>
+        <v>0.1314</v>
       </c>
       <c r="V3" t="n">
         <v>3.3584</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8406</v>
+        <v>3.6293</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6207</v>
+        <v>3.5774</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2199</v>
+        <v>0.0519</v>
       </c>
       <c r="G4" t="n">
         <v>2.4377</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8667</v>
+        <v>0.6554</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7275</v>
+        <v>0.6842</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1393</v>
+        <v>-0.0288</v>
       </c>
       <c r="V4" t="n">
         <v>0.5361</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7581</v>
+        <v>1.5242</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6982</v>
+        <v>-0.2264</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4563</v>
+        <v>1.7506</v>
       </c>
       <c r="G5" t="n">
         <v>1.2997</v>
@@ -844,13 +844,13 @@
         <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7736</v>
+        <v>-1.0075</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>-0.5737</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2719</v>
+        <v>-0.4338</v>
       </c>
       <c r="V5" t="n">
         <v>0.5361</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.643</v>
+        <v>0.7587</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4325</v>
+        <v>-0.9384</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0755</v>
+        <v>1.6971</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1838</v>
+        <v>-3.2897</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6015</v>
+        <v>0.3241</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5822000000000001</v>
+        <v>-3.6138</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7728</v>
+        <v>-3.4293</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3948</v>
+        <v>0.0742</v>
       </c>
       <c r="L6" t="n">
-        <v>0.378</v>
+        <v>-3.5035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.411</v>
+        <v>0.1396</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2067</v>
+        <v>0.2499</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2042</v>
+        <v>-0.1103</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1551</v>
+        <v>-0.3253</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1142</v>
+        <v>0.2047</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0409</v>
+        <v>-0.53</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>2.2862</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.2862</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.516</v>
+        <v>0.4912</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0131</v>
+        <v>-0.6034</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5291</v>
+        <v>1.0946</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2897</v>
+        <v>1.1822</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3241</v>
+        <v>0.9113</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6138</v>
+        <v>0.2709</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.4293</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0742</v>
+        <v>0.8401999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.5035</v>
+        <v>-0.0403</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1396</v>
+        <v>0.3823</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2499</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1103</v>
+        <v>0.3113</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.923</v>
       </c>
       <c r="T7" t="n">
-        <v>0.13</v>
+        <v>-0.2436</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.698</v>
+        <v>-0.6794</v>
       </c>
       <c r="V7" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.2862</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1651</v>
+        <v>0.2391</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9573</v>
+        <v>-0.6684</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7922</v>
+        <v>0.9075</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1822</v>
+        <v>2.1838</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9113</v>
+        <v>1.6015</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2709</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7999000000000001</v>
+        <v>1.7728</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8401999999999999</v>
+        <v>1.3948</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0403</v>
+        <v>0.378</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3823</v>
+        <v>0.411</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.2067</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3113</v>
+        <v>0.2042</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5793</v>
+        <v>-0.2489</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5975</v>
+        <v>-0.1217</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9818</v>
+        <v>-0.1272</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="9">
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9611</v>
+        <v>-0.6391</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8628</v>
+        <v>-2.1093</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0983</v>
+        <v>1.4702</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2857</v>
+        <v>-0.5505</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6567</v>
+        <v>0.1154</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6291</v>
+        <v>-0.6659</v>
       </c>
       <c r="J10" t="n">
-        <v>0.521</v>
+        <v>-1.7586</v>
       </c>
       <c r="K10" t="n">
-        <v>0.521</v>
+        <v>-0.4166</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-1.3419</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7648</v>
+        <v>1.2081</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1357</v>
+        <v>0.5321</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6291</v>
+        <v>0.6761</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2469</v>
+        <v>-1.3928</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.224</v>
+        <v>-0.2631</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0228</v>
+        <v>-1.1297</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0722</v>
+        <v>1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4785</v>
+        <v>-0.7595</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5354</v>
+        <v>-0.8628</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0569</v>
+        <v>0.1033</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5693</v>
+        <v>1.2857</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8102</v>
+        <v>0.6567</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2409</v>
+        <v>0.6291</v>
       </c>
       <c r="J11" t="n">
-        <v>2.2268</v>
+        <v>0.521</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8856</v>
+        <v>0.521</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3412</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6576</v>
+        <v>0.7648</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0755</v>
+        <v>0.1357</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5821</v>
+        <v>0.6291</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3519</v>
+        <v>-0.0452</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2829</v>
+        <v>-0.224</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1788</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5617</v>
+        <v>-1.0317</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7447</v>
+        <v>-2.0802</v>
       </c>
       <c r="F12" t="n">
-        <v>1.183</v>
+        <v>1.0485</v>
       </c>
       <c r="G12" t="n">
         <v>0.1963</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.593</v>
+        <v>-0.063</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6563</v>
+        <v>0.0081</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0633</v>
+        <v>-0.0712</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8608</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.9256</v>
+        <v>-1.0745</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8917</v>
+        <v>-1.2995</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9661</v>
+        <v>0.2249</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5505</v>
+        <v>1.5693</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1154</v>
+        <v>1.8102</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6659</v>
+        <v>-0.2409</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.7586</v>
+        <v>2.2268</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4166</v>
+        <v>1.8856</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3419</v>
+        <v>0.3412</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2081</v>
+        <v>-0.6576</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5321</v>
+        <v>-0.0755</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6761</v>
+        <v>-0.5821</v>
       </c>
       <c r="P13" t="n">
-        <v>0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.6793</v>
+        <v>0.0521</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0455</v>
+        <v>-0.047</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.6337</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>16.3873</v>
+        <v>16.7608</v>
       </c>
       <c r="E14" t="n">
-        <v>4.972500000000002</v>
+        <v>5.3461</v>
       </c>
       <c r="F14" t="n">
-        <v>11.4147</v>
+        <v>11.4146</v>
       </c>
       <c r="G14" t="n">
         <v>12.8491</v>
@@ -1522,7 +1522,7 @@
         <v>10.0963</v>
       </c>
       <c r="K14" t="n">
-        <v>7.153099999999999</v>
+        <v>7.1531</v>
       </c>
       <c r="L14" t="n">
         <v>2.9432</v>
@@ -1534,7 +1534,7 @@
         <v>2.283</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4699</v>
+        <v>0.4698999999999999</v>
       </c>
       <c r="P14" t="n">
         <v>2.319700000000001</v>
@@ -1546,16 +1546,16 @@
         <v>16.2368</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.6374</v>
+        <v>-3.2639</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3514</v>
+        <v>0.02199999999999992</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.2857</v>
+        <v>-3.286</v>
       </c>
       <c r="V14" t="n">
-        <v>4.855999999999998</v>
+        <v>4.856</v>
       </c>
       <c r="W14" t="n">
         <v>9.1448</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1256</v>
+        <v>2.0927</v>
       </c>
       <c r="E15" t="n">
-        <v>3.6186</v>
+        <v>3.8545</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.493</v>
+        <v>-1.7618</v>
       </c>
       <c r="G15" t="n">
         <v>2.7821</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0394</v>
+        <v>1.0064</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5113</v>
+        <v>0.7472</v>
       </c>
       <c r="U15" t="n">
-        <v>0.528</v>
+        <v>0.2592</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>E. JACKSON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3524</v>
+        <v>1.6449</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3318</v>
+        <v>2.1542</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6842</v>
+        <v>-0.5093</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.2336</v>
+        <v>-0.2913</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4502</v>
+        <v>-1.6364</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.7833</v>
+        <v>1.3451</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.3545</v>
+        <v>2.3961</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1078</v>
+        <v>-0.7423</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4623</v>
+        <v>3.1383</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8791</v>
+        <v>-2.6874</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5581</v>
+        <v>-0.8942</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3211</v>
+        <v>-1.7933</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8901</v>
+        <v>0.3796</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1824</v>
+        <v>0.3817</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7077</v>
+        <v>-0.0022</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.3247</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. JACKSON</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8928</v>
+        <v>0.2811</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9183</v>
+        <v>-1.728</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0255</v>
+        <v>2.0091</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2913</v>
+        <v>0.4265</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6364</v>
+        <v>-1.0892</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3451</v>
+        <v>1.5157</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3961</v>
+        <v>0.0762</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7423</v>
+        <v>-1.0245</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1383</v>
+        <v>1.1006</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.6874</v>
+        <v>0.3503</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8942</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7933</v>
+        <v>0.415</v>
       </c>
       <c r="P17" t="n">
-        <v>0.232</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3725</v>
+        <v>0.7824</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1458</v>
+        <v>0.5153</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5184</v>
+        <v>0.2671</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3247</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5382</v>
+        <v>-0.4162</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9639</v>
+        <v>-1.8652</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4258</v>
+        <v>1.449</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4265</v>
+        <v>-2.2336</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0892</v>
+        <v>-0.4502</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5157</v>
+        <v>-1.7833</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0762</v>
+        <v>-1.3545</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0245</v>
+        <v>0.1078</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1006</v>
+        <v>-1.4623</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3503</v>
+        <v>-0.8791</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.5581</v>
       </c>
       <c r="O18" t="n">
-        <v>0.415</v>
+        <v>-0.3211</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0369</v>
+        <v>1.1215</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2794</v>
+        <v>0.6491</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3163</v>
+        <v>0.4725</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8658</v>
+        <v>-0.4283</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1131</v>
+        <v>-1.8772</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2473</v>
+        <v>1.449</v>
       </c>
       <c r="G19" t="n">
         <v>-0.48</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1502</v>
+        <v>0.5878</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2126</v>
+        <v>0.4485</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0624</v>
+        <v>0.1393</v>
       </c>
       <c r="V19" t="n">
         <v>-0.5361</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3731</v>
+        <v>-1.2215</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4818</v>
+        <v>-1.3639</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1087</v>
+        <v>0.1423</v>
       </c>
       <c r="G20" t="n">
         <v>0.1119</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1955</v>
+        <v>0.347</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0193</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2148</v>
+        <v>0.2484</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1444</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6467</v>
+        <v>-1.8882</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8056</v>
+        <v>-0.9799</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8411</v>
+        <v>-0.9083</v>
       </c>
       <c r="G21" t="n">
         <v>-5.5198</v>
@@ -2092,13 +2092,13 @@
         <v>1.6237</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8074</v>
+        <v>-0.049</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8804</v>
+        <v>-0.0547</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0057</v>
       </c>
       <c r="V21" t="n">
         <v>3.2166</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. VAUTIER</t>
+          <t>M. AJINCA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9043</v>
+        <v>-3.016</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2711</v>
+        <v>-2.0365</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3669</v>
+        <v>-0.9795</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3787</v>
+        <v>-1.8216</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2918</v>
+        <v>-0.3193</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-1.5023</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6924</v>
+        <v>-0.6959</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7661</v>
+        <v>0.0168</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0736</v>
+        <v>-0.7127</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6862</v>
+        <v>-1.1257</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.3361</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1605</v>
+        <v>-0.7896</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7834</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>1.3996</v>
+        <v>-0.1248</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9006</v>
+        <v>-0.1808</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4991</v>
+        <v>0.056</v>
       </c>
       <c r="V22" t="n">
         <v>-0.1418</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. AJINCA</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4821</v>
+        <v>-3.6144</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1544</v>
+        <v>0.8731</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3277</v>
+        <v>-4.4875</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8216</v>
+        <v>-2.8025</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3193</v>
+        <v>-1.2699</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5023</v>
+        <v>-1.5326</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6959</v>
+        <v>0.2713</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0168</v>
+        <v>0.1176</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7127</v>
+        <v>0.1536</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1257</v>
+        <v>-3.0738</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3361</v>
+        <v>-1.3875</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7896</v>
+        <v>-1.6862</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5909</v>
+        <v>0.4769</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2987</v>
+        <v>0.6018</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2921</v>
+        <v>-0.125</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1418</v>
+        <v>-2.6805</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>B. VAUTIER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4344</v>
+        <v>-3.6335</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4013</v>
+        <v>-3.9788</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8357</v>
+        <v>0.3453</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8025</v>
+        <v>-1.3787</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2699</v>
+        <v>-1.2918</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5326</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2713</v>
+        <v>-0.6924</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1176</v>
+        <v>-0.7661</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1536</v>
+        <v>0.0736</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0738</v>
+        <v>-0.6862</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.3875</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6862</v>
+        <v>-0.1605</v>
       </c>
       <c r="P24" t="n">
-        <v>1.3917</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3431</v>
+        <v>0.6704</v>
       </c>
       <c r="T24" t="n">
-        <v>0.13</v>
+        <v>0.1928</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4731</v>
+        <v>0.4775</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.6805</v>
+        <v>-0.1418</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.6805</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5134</v>
+        <v>-4.6149</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.1587</v>
+        <v>-3.3946</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3547</v>
+        <v>-1.2203</v>
       </c>
       <c r="G25" t="n">
         <v>-1.6421</v>
@@ -2404,13 +2404,13 @@
         <v>1.3917</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1133</v>
+        <v>0.0119</v>
       </c>
       <c r="T25" t="n">
-        <v>0.1221</v>
+        <v>-0.1138</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.1256</v>
       </c>
       <c r="V25" t="n">
         <v>-3.2166</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-16.3872</v>
+        <v>-14.8143</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.3422</v>
+        <v>-10.3423</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.0448</v>
+        <v>-4.472</v>
       </c>
       <c r="G26" t="n">
         <v>-12.8491</v>
@@ -2455,13 +2455,13 @@
         <v>-3.4127</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.752600000000001</v>
+        <v>-2.7526</v>
       </c>
       <c r="K26" t="n">
         <v>-2.2831</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4698999999999997</v>
+        <v>-0.4698999999999994</v>
       </c>
       <c r="M26" t="n">
         <v>-10.0964</v>
@@ -2482,13 +2482,13 @@
         <v>13.9173</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6373</v>
+        <v>5.210099999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.2858</v>
+        <v>3.2857</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3513999999999999</v>
+        <v>1.9241</v>
       </c>
       <c r="V26" t="n">
         <v>-4.856</v>
